--- a/artfynd/A 5361-2026 artfynd.xlsx
+++ b/artfynd/A 5361-2026 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>134253243</v>
       </c>
       <c r="B5" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 5361-2026 artfynd.xlsx
+++ b/artfynd/A 5361-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134253330</v>
+        <v>134253184</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>99001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>223049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>801289</v>
+        <v>801379</v>
       </c>
       <c r="R2" t="n">
-        <v>7156580</v>
+        <v>7156483</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +756,13 @@
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,42 +781,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134253385</v>
+        <v>134253224</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>99001</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>223049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801355</v>
+        <v>801366</v>
       </c>
       <c r="R3" t="n">
-        <v>7156586</v>
+        <v>7156494</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,17 +862,13 @@
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,42 +887,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134253411</v>
+        <v>134253230</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>99001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>223049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -938,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>801391</v>
+        <v>801363</v>
       </c>
       <c r="R4" t="n">
-        <v>7156650</v>
+        <v>7156500</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,15 +970,16 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>Rik förekomst!</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1005,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134253243</v>
+        <v>134253424</v>
       </c>
       <c r="B5" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,31 +1009,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>801331</v>
+        <v>801405</v>
       </c>
       <c r="R5" t="n">
-        <v>7156517</v>
+        <v>7156691</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,11 +1078,6 @@
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ett tiotal bladrosetter</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1113,6 +1100,447 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134253330</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fjällmorberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>801289</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7156580</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134253385</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fjällmorberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>801355</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7156586</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134253411</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fjällmorberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>801391</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7156650</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134253243</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fjällmorberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>801331</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7156517</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ett tiotal bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5361-2026 artfynd.xlsx
+++ b/artfynd/A 5361-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134253424</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134253330</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134253385</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134253411</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134253243</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134253184</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1430,6 +1465,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134253224</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1541,8 +1581,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134253230</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>